--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486675_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486675_PROCESSED_CHRONO.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>A. CASTELANOS POLA</t>
+          <t>J. KASA</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>8.6182</v>
+        <v>8.033799999999999</v>
       </c>
       <c r="E2" t="n">
-        <v>2.7147</v>
+        <v>4.4071</v>
       </c>
       <c r="F2" t="n">
-        <v>5.9035</v>
+        <v>3.6267</v>
       </c>
       <c r="G2" t="n">
-        <v>3.4077</v>
+        <v>5.7992</v>
       </c>
       <c r="H2" t="n">
-        <v>1.7371</v>
+        <v>-0.3589</v>
       </c>
       <c r="I2" t="n">
-        <v>1.6707</v>
+        <v>6.1581</v>
       </c>
       <c r="J2" t="n">
-        <v>0.0301</v>
+        <v>3.3177</v>
       </c>
       <c r="K2" t="n">
-        <v>-0.2616</v>
+        <v>-2.013</v>
       </c>
       <c r="L2" t="n">
-        <v>0.2917</v>
+        <v>5.3307</v>
       </c>
       <c r="M2" t="n">
-        <v>3.3776</v>
+        <v>2.4815</v>
       </c>
       <c r="N2" t="n">
-        <v>1.9986</v>
+        <v>1.6541</v>
       </c>
       <c r="O2" t="n">
-        <v>1.379</v>
+        <v>0.8274</v>
       </c>
       <c r="P2" t="n">
-        <v>0.9654</v>
+        <v>0.3862</v>
       </c>
       <c r="Q2" t="n">
         <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>0.9654</v>
+        <v>0.3862</v>
       </c>
       <c r="S2" t="n">
-        <v>3.9169</v>
+        <v>0.6208</v>
       </c>
       <c r="T2" t="n">
-        <v>2.3989</v>
+        <v>-0.1383</v>
       </c>
       <c r="U2" t="n">
-        <v>1.5179</v>
+        <v>0.7591</v>
       </c>
       <c r="V2" t="n">
-        <v>0.3282</v>
+        <v>1.2277</v>
       </c>
       <c r="W2" t="n">
-        <v>0.2856</v>
+        <v>1.2277</v>
       </c>
       <c r="X2" t="n">
-        <v>0.0426</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>J. KASA</t>
+          <t>M. OLIVA I CAMPABADAL</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,58 +643,58 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>8.3566</v>
+        <v>7.0429</v>
       </c>
       <c r="E3" t="n">
-        <v>4.4071</v>
+        <v>4.5335</v>
       </c>
       <c r="F3" t="n">
-        <v>3.9495</v>
+        <v>2.5094</v>
       </c>
       <c r="G3" t="n">
-        <v>5.7992</v>
+        <v>5.1048</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.3589</v>
+        <v>1.4199</v>
       </c>
       <c r="I3" t="n">
-        <v>6.1581</v>
+        <v>3.6849</v>
       </c>
       <c r="J3" t="n">
-        <v>3.3177</v>
+        <v>3.7129</v>
       </c>
       <c r="K3" t="n">
-        <v>-2.013</v>
+        <v>0.4552</v>
       </c>
       <c r="L3" t="n">
-        <v>5.3307</v>
+        <v>3.2577</v>
       </c>
       <c r="M3" t="n">
-        <v>2.4815</v>
+        <v>1.3919</v>
       </c>
       <c r="N3" t="n">
-        <v>1.6541</v>
+        <v>0.9646</v>
       </c>
       <c r="O3" t="n">
-        <v>0.8274</v>
+        <v>0.4272</v>
       </c>
       <c r="P3" t="n">
-        <v>0.3862</v>
+        <v>1.1585</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>0.3862</v>
+        <v>1.1585</v>
       </c>
       <c r="S3" t="n">
-        <v>0.9436</v>
+        <v>-0.448</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.1383</v>
+        <v>-0.4071</v>
       </c>
       <c r="U3" t="n">
-        <v>1.0819</v>
+        <v>-0.0409</v>
       </c>
       <c r="V3" t="n">
         <v>1.2277</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>M. OLIVA I CAMPABADAL</t>
+          <t>P. LOPEZ USO</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,64 +721,64 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>6.6581</v>
+        <v>6.2732</v>
       </c>
       <c r="E4" t="n">
-        <v>4.2232</v>
+        <v>3.171</v>
       </c>
       <c r="F4" t="n">
-        <v>2.4349</v>
+        <v>3.1022</v>
       </c>
       <c r="G4" t="n">
-        <v>5.1048</v>
+        <v>5.5629</v>
       </c>
       <c r="H4" t="n">
-        <v>1.4199</v>
+        <v>4.2335</v>
       </c>
       <c r="I4" t="n">
-        <v>3.6849</v>
+        <v>1.3293</v>
       </c>
       <c r="J4" t="n">
-        <v>3.7129</v>
+        <v>3.5507</v>
       </c>
       <c r="K4" t="n">
-        <v>0.4552</v>
+        <v>2.6486</v>
       </c>
       <c r="L4" t="n">
-        <v>3.2577</v>
+        <v>0.9021</v>
       </c>
       <c r="M4" t="n">
-        <v>1.3919</v>
+        <v>2.0122</v>
       </c>
       <c r="N4" t="n">
-        <v>0.9646</v>
+        <v>1.5849</v>
       </c>
       <c r="O4" t="n">
         <v>0.4272</v>
       </c>
       <c r="P4" t="n">
-        <v>1.1585</v>
+        <v>0.7723</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>1.1585</v>
+        <v>0.7723</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.8328</v>
+        <v>-0.062</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.7174</v>
+        <v>-0.3797</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.1154</v>
+        <v>0.3177</v>
       </c>
       <c r="V4" t="n">
-        <v>1.2277</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>1.2277</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>N. CEBRIAN HERNANDEZ</t>
+          <t>A. CASTELANOS POLA</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>5.3279</v>
+        <v>6.26</v>
       </c>
       <c r="E5" t="n">
-        <v>4.1786</v>
+        <v>0.8531</v>
       </c>
       <c r="F5" t="n">
-        <v>1.1493</v>
+        <v>5.4069</v>
       </c>
       <c r="G5" t="n">
-        <v>6.9264</v>
+        <v>3.4077</v>
       </c>
       <c r="H5" t="n">
-        <v>0.5717</v>
+        <v>1.7371</v>
       </c>
       <c r="I5" t="n">
-        <v>6.3547</v>
+        <v>1.6707</v>
       </c>
       <c r="J5" t="n">
-        <v>4.9966</v>
+        <v>0.0301</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.2549</v>
+        <v>-0.2616</v>
       </c>
       <c r="L5" t="n">
-        <v>5.2516</v>
+        <v>0.2917</v>
       </c>
       <c r="M5" t="n">
-        <v>1.9298</v>
+        <v>3.3776</v>
       </c>
       <c r="N5" t="n">
-        <v>0.8266</v>
+        <v>1.9986</v>
       </c>
       <c r="O5" t="n">
-        <v>1.1032</v>
+        <v>1.379</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.7723</v>
+        <v>0.9654</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.9654</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>0.1931</v>
+        <v>0.9654</v>
       </c>
       <c r="S5" t="n">
-        <v>0.1159</v>
+        <v>1.5586</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.1383</v>
+        <v>0.5373</v>
       </c>
       <c r="U5" t="n">
-        <v>0.2541</v>
+        <v>1.0213</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.9421</v>
+        <v>0.3282</v>
       </c>
       <c r="W5" t="n">
         <v>0.2856</v>
       </c>
       <c r="X5" t="n">
-        <v>-1.2277</v>
+        <v>0.0426</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>P. LOPEZ USO</t>
+          <t>N. CEBRIAN HERNANDEZ</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>5.1768</v>
+        <v>5.5017</v>
       </c>
       <c r="E6" t="n">
-        <v>2.4471</v>
+        <v>4.1786</v>
       </c>
       <c r="F6" t="n">
-        <v>2.7297</v>
+        <v>1.3231</v>
       </c>
       <c r="G6" t="n">
-        <v>5.5629</v>
+        <v>6.9264</v>
       </c>
       <c r="H6" t="n">
-        <v>4.2335</v>
+        <v>0.5717</v>
       </c>
       <c r="I6" t="n">
-        <v>1.3293</v>
+        <v>6.3547</v>
       </c>
       <c r="J6" t="n">
-        <v>3.5507</v>
+        <v>4.9966</v>
       </c>
       <c r="K6" t="n">
-        <v>2.6486</v>
+        <v>-0.2549</v>
       </c>
       <c r="L6" t="n">
-        <v>0.9021</v>
+        <v>5.2516</v>
       </c>
       <c r="M6" t="n">
-        <v>2.0122</v>
+        <v>1.9298</v>
       </c>
       <c r="N6" t="n">
-        <v>1.5849</v>
+        <v>0.8266</v>
       </c>
       <c r="O6" t="n">
-        <v>0.4272</v>
+        <v>1.1032</v>
       </c>
       <c r="P6" t="n">
-        <v>0.7723</v>
+        <v>-0.7723</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>-0.9654</v>
       </c>
       <c r="R6" t="n">
-        <v>0.7723</v>
+        <v>0.1931</v>
       </c>
       <c r="S6" t="n">
-        <v>-1.1584</v>
+        <v>0.2897</v>
       </c>
       <c r="T6" t="n">
-        <v>-1.1036</v>
+        <v>-0.1383</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.0548</v>
+        <v>0.428</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>-0.9421</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>0.2856</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>-1.2277</v>
       </c>
     </row>
     <row r="7">
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>5.0906</v>
+        <v>4.6106</v>
       </c>
       <c r="E7" t="n">
-        <v>2.41</v>
+        <v>2.2031</v>
       </c>
       <c r="F7" t="n">
-        <v>2.6806</v>
+        <v>2.4075</v>
       </c>
       <c r="G7" t="n">
         <v>2.0821</v>
@@ -1000,13 +1000,13 @@
         <v>0.9654</v>
       </c>
       <c r="S7" t="n">
-        <v>0.8387</v>
+        <v>0.3587</v>
       </c>
       <c r="T7" t="n">
-        <v>0.1377</v>
+        <v>-0.0692</v>
       </c>
       <c r="U7" t="n">
-        <v>0.7010999999999999</v>
+        <v>0.4279</v>
       </c>
       <c r="V7" t="n">
         <v>2.1698</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>3.9958</v>
+        <v>4.6081</v>
       </c>
       <c r="E8" t="n">
-        <v>1.9705</v>
+        <v>2.3842</v>
       </c>
       <c r="F8" t="n">
-        <v>2.0252</v>
+        <v>2.2239</v>
       </c>
       <c r="G8" t="n">
         <v>5.5005</v>
@@ -1078,13 +1078,13 @@
         <v>0.1931</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.4468</v>
+        <v>0.1655</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.7725</v>
+        <v>-0.3589</v>
       </c>
       <c r="U8" t="n">
-        <v>0.3258</v>
+        <v>0.5244</v>
       </c>
       <c r="V8" t="n">
         <v>-0.2856</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>2.8109</v>
+        <v>3.2494</v>
       </c>
       <c r="E9" t="n">
-        <v>1.2297</v>
+        <v>1.6433</v>
       </c>
       <c r="F9" t="n">
-        <v>1.5812</v>
+        <v>1.606</v>
       </c>
       <c r="G9" t="n">
         <v>2.9937</v>
@@ -1156,13 +1156,13 @@
         <v>1.3515</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.4797</v>
+        <v>-0.0412</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.5518</v>
+        <v>-0.1381</v>
       </c>
       <c r="U9" t="n">
-        <v>0.0721</v>
+        <v>0.0969</v>
       </c>
       <c r="V9" t="n">
         <v>1.8415</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.0202</v>
+        <v>0.0543</v>
       </c>
       <c r="E10" t="n">
         <v>-0.0697</v>
       </c>
       <c r="F10" t="n">
-        <v>0.0495</v>
+        <v>0.124</v>
       </c>
       <c r="G10" t="n">
         <v>0.3163</v>
@@ -1234,13 +1234,13 @@
         <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.3365</v>
+        <v>-0.262</v>
       </c>
       <c r="T10" t="n">
         <v>-0.1104</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.2261</v>
+        <v>-0.1516</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.7444</v>
+        <v>-0.3637</v>
       </c>
       <c r="E11" t="n">
-        <v>0.4787</v>
+        <v>0.6855</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.2231</v>
+        <v>-1.0492</v>
       </c>
       <c r="G11" t="n">
         <v>0.7534</v>
@@ -1312,13 +1312,13 @@
         <v>0.7723</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.0425</v>
+        <v>-0.6618000000000001</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.6622</v>
+        <v>-0.4553</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.3803</v>
+        <v>-0.2065</v>
       </c>
       <c r="V11" t="n">
         <v>-1.2277</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>45.27030000000001</v>
+        <v>45.2703</v>
       </c>
       <c r="E12" t="n">
-        <v>23.9899</v>
+        <v>23.9897</v>
       </c>
       <c r="F12" t="n">
-        <v>21.2803</v>
+        <v>21.2805</v>
       </c>
       <c r="G12" t="n">
         <v>38.447</v>
@@ -1366,7 +1366,7 @@
         <v>23.2171</v>
       </c>
       <c r="K12" t="n">
-        <v>-1.7186</v>
+        <v>-1.718599999999999</v>
       </c>
       <c r="L12" t="n">
         <v>24.9357</v>
@@ -1384,19 +1384,19 @@
         <v>0.9655</v>
       </c>
       <c r="Q12" t="n">
-        <v>-5.7924</v>
+        <v>-5.792400000000001</v>
       </c>
       <c r="R12" t="n">
         <v>6.7578</v>
       </c>
       <c r="S12" t="n">
-        <v>1.5184</v>
+        <v>1.5183</v>
       </c>
       <c r="T12" t="n">
-        <v>-1.657900000000001</v>
+        <v>-1.658</v>
       </c>
       <c r="U12" t="n">
-        <v>3.1763</v>
+        <v>3.176299999999999</v>
       </c>
       <c r="V12" t="n">
         <v>4.339499999999999</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-2.0441</v>
+        <v>-2.1516</v>
       </c>
       <c r="E13" t="n">
-        <v>-1.2963</v>
+        <v>-1.5031</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.7478</v>
+        <v>-0.6485</v>
       </c>
       <c r="G13" t="n">
         <v>-1.5308</v>
@@ -1468,13 +1468,13 @@
         <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>0.4521</v>
+        <v>0.3446</v>
       </c>
       <c r="T13" t="n">
-        <v>0.3859</v>
+        <v>0.1791</v>
       </c>
       <c r="U13" t="n">
-        <v>0.06619999999999999</v>
+        <v>0.1655</v>
       </c>
       <c r="V13" t="n">
         <v>0</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-2.9477</v>
+        <v>-2.4099</v>
       </c>
       <c r="E14" t="n">
-        <v>-2.5651</v>
+        <v>-2.1515</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.3826</v>
+        <v>-0.2584</v>
       </c>
       <c r="G14" t="n">
         <v>-2.0276</v>
@@ -1546,13 +1546,13 @@
         <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.6345</v>
+        <v>-0.09660000000000001</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.5795</v>
+        <v>-0.1658</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.055</v>
+        <v>0.0692</v>
       </c>
       <c r="V14" t="n">
         <v>-0.2856</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>P. DIOP</t>
+          <t>A. PEREZ GALVAN</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>-3.1261</v>
+        <v>-3.029</v>
       </c>
       <c r="E15" t="n">
-        <v>1.1782</v>
+        <v>-0.3505</v>
       </c>
       <c r="F15" t="n">
-        <v>-4.3043</v>
+        <v>-2.6784</v>
       </c>
       <c r="G15" t="n">
-        <v>-4.3258</v>
+        <v>-1.1174</v>
       </c>
       <c r="H15" t="n">
-        <v>-1.6966</v>
+        <v>3.4967</v>
       </c>
       <c r="I15" t="n">
-        <v>-2.6292</v>
+        <v>-4.614</v>
       </c>
       <c r="J15" t="n">
-        <v>-0.6008</v>
+        <v>1.7737</v>
       </c>
       <c r="K15" t="n">
-        <v>-1.2134</v>
+        <v>3.1526</v>
       </c>
       <c r="L15" t="n">
-        <v>0.6127</v>
+        <v>-1.379</v>
       </c>
       <c r="M15" t="n">
-        <v>-3.725</v>
+        <v>-2.891</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.4832</v>
+        <v>0.344</v>
       </c>
       <c r="O15" t="n">
-        <v>-3.2418</v>
+        <v>-3.2351</v>
       </c>
       <c r="P15" t="n">
-        <v>0.5792</v>
+        <v>-1.3515</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>-1.9308</v>
       </c>
       <c r="R15" t="n">
         <v>0.5792</v>
       </c>
       <c r="S15" t="n">
-        <v>0.8659</v>
+        <v>-0.7655</v>
       </c>
       <c r="T15" t="n">
-        <v>0.5512</v>
+        <v>-0.8073</v>
       </c>
       <c r="U15" t="n">
-        <v>0.3147</v>
+        <v>0.0417</v>
       </c>
       <c r="V15" t="n">
-        <v>-0.2455</v>
+        <v>0.2055</v>
       </c>
       <c r="W15" t="n">
-        <v>1.2277</v>
+        <v>0.6138</v>
       </c>
       <c r="X15" t="n">
-        <v>-1.4732</v>
+        <v>-0.4084</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A. PEREZ GALVAN</t>
+          <t>J. BARRIOS RUIZ</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-3.5709</v>
+        <v>-3.4854</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.8676</v>
+        <v>-2.4686</v>
       </c>
       <c r="F16" t="n">
-        <v>-2.7033</v>
+        <v>-1.0168</v>
       </c>
       <c r="G16" t="n">
-        <v>-1.1174</v>
+        <v>-1.9172</v>
       </c>
       <c r="H16" t="n">
-        <v>3.4967</v>
+        <v>-0.5517</v>
       </c>
       <c r="I16" t="n">
-        <v>-4.614</v>
+        <v>-1.3654</v>
       </c>
       <c r="J16" t="n">
-        <v>1.7737</v>
+        <v>-1.379</v>
       </c>
       <c r="K16" t="n">
-        <v>3.1526</v>
+        <v>-0.6895</v>
       </c>
       <c r="L16" t="n">
-        <v>-1.379</v>
+        <v>-0.6895</v>
       </c>
       <c r="M16" t="n">
-        <v>-2.891</v>
+        <v>-0.5382</v>
       </c>
       <c r="N16" t="n">
-        <v>0.344</v>
+        <v>0.1377</v>
       </c>
       <c r="O16" t="n">
-        <v>-3.2351</v>
+        <v>-0.6758999999999999</v>
       </c>
       <c r="P16" t="n">
-        <v>-1.3515</v>
+        <v>-0.9654</v>
       </c>
       <c r="Q16" t="n">
-        <v>-1.9308</v>
+        <v>-0.9654</v>
       </c>
       <c r="R16" t="n">
-        <v>0.5792</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>-1.3075</v>
+        <v>-0.3173</v>
       </c>
       <c r="T16" t="n">
-        <v>-1.3244</v>
+        <v>-0.1242</v>
       </c>
       <c r="U16" t="n">
-        <v>0.0169</v>
+        <v>-0.193</v>
       </c>
       <c r="V16" t="n">
-        <v>0.2055</v>
+        <v>-0.2856</v>
       </c>
       <c r="W16" t="n">
-        <v>0.6138</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.4084</v>
+        <v>-0.2856</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>M. PEREZ CHAFINO</t>
+          <t>P. DIOP</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-3.7047</v>
+        <v>-3.8957</v>
       </c>
       <c r="E17" t="n">
-        <v>-1.7105</v>
+        <v>0.5576</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.9942</v>
+        <v>-4.4533</v>
       </c>
       <c r="G17" t="n">
-        <v>-4.2971</v>
+        <v>-4.3258</v>
       </c>
       <c r="H17" t="n">
-        <v>0.2491</v>
+        <v>-1.6966</v>
       </c>
       <c r="I17" t="n">
-        <v>-4.5462</v>
+        <v>-2.6292</v>
       </c>
       <c r="J17" t="n">
-        <v>-2.151</v>
+        <v>-0.6008</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.164</v>
+        <v>-1.2134</v>
       </c>
       <c r="L17" t="n">
-        <v>-1.9871</v>
+        <v>0.6127</v>
       </c>
       <c r="M17" t="n">
-        <v>-2.1461</v>
+        <v>-3.725</v>
       </c>
       <c r="N17" t="n">
-        <v>0.4131</v>
+        <v>-0.4832</v>
       </c>
       <c r="O17" t="n">
-        <v>-2.5591</v>
+        <v>-3.2418</v>
       </c>
       <c r="P17" t="n">
-        <v>0.1931</v>
+        <v>0.5792</v>
       </c>
       <c r="Q17" t="n">
-        <v>-0.9654</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>1.1585</v>
+        <v>0.5792</v>
       </c>
       <c r="S17" t="n">
-        <v>3.1002</v>
+        <v>0.0964</v>
       </c>
       <c r="T17" t="n">
-        <v>1.4059</v>
+        <v>-0.0693</v>
       </c>
       <c r="U17" t="n">
-        <v>1.6943</v>
+        <v>0.1657</v>
       </c>
       <c r="V17" t="n">
-        <v>-2.7009</v>
+        <v>-0.2455</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>1.2277</v>
       </c>
       <c r="X17" t="n">
-        <v>-2.7009</v>
+        <v>-1.4732</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>J. BARRIOS RUIZ</t>
+          <t>M. ABITBOL VIERA</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-3.7419</v>
+        <v>-4.6697</v>
       </c>
       <c r="E18" t="n">
-        <v>-2.6754</v>
+        <v>-1.4284</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.0665</v>
+        <v>-3.2412</v>
       </c>
       <c r="G18" t="n">
-        <v>-1.9172</v>
+        <v>-3.657</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.5517</v>
+        <v>-1.1793</v>
       </c>
       <c r="I18" t="n">
-        <v>-1.3654</v>
+        <v>-2.4777</v>
       </c>
       <c r="J18" t="n">
-        <v>-1.379</v>
+        <v>-0.5659999999999999</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.6895</v>
+        <v>-1.1787</v>
       </c>
       <c r="L18" t="n">
-        <v>-0.6895</v>
+        <v>0.6127</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.5382</v>
+        <v>-3.091</v>
       </c>
       <c r="N18" t="n">
-        <v>0.1377</v>
+        <v>-0.0005999999999999999</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.6758999999999999</v>
+        <v>-3.0904</v>
       </c>
       <c r="P18" t="n">
-        <v>-0.9654</v>
+        <v>0.9654</v>
       </c>
       <c r="Q18" t="n">
-        <v>-0.9654</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>0.9654</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.5738</v>
+        <v>-0.6276</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.3311</v>
+        <v>-0.8624000000000001</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.2427</v>
+        <v>0.2349</v>
       </c>
       <c r="V18" t="n">
-        <v>-0.2856</v>
+        <v>-1.3505</v>
       </c>
       <c r="W18" t="n">
         <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.2856</v>
+        <v>-1.3505</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>M. ABITBOL VIERA</t>
+          <t>M. PEREZ CHAFINO</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-5.162</v>
+        <v>-5.819</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.9456</v>
+        <v>-3.055</v>
       </c>
       <c r="F19" t="n">
-        <v>-3.2164</v>
+        <v>-2.764</v>
       </c>
       <c r="G19" t="n">
-        <v>-3.657</v>
+        <v>-4.2971</v>
       </c>
       <c r="H19" t="n">
-        <v>-1.1793</v>
+        <v>0.2491</v>
       </c>
       <c r="I19" t="n">
-        <v>-2.4777</v>
+        <v>-4.5462</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.5659999999999999</v>
+        <v>-2.151</v>
       </c>
       <c r="K19" t="n">
-        <v>-1.1787</v>
+        <v>-0.164</v>
       </c>
       <c r="L19" t="n">
-        <v>0.6127</v>
+        <v>-1.9871</v>
       </c>
       <c r="M19" t="n">
-        <v>-3.091</v>
+        <v>-2.1461</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.0005999999999999999</v>
+        <v>0.4131</v>
       </c>
       <c r="O19" t="n">
-        <v>-3.0904</v>
+        <v>-2.5591</v>
       </c>
       <c r="P19" t="n">
-        <v>0.9654</v>
+        <v>0.1931</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>-0.9654</v>
       </c>
       <c r="R19" t="n">
-        <v>0.9654</v>
+        <v>1.1585</v>
       </c>
       <c r="S19" t="n">
-        <v>-1.1198</v>
+        <v>0.9859</v>
       </c>
       <c r="T19" t="n">
-        <v>-1.3796</v>
+        <v>0.0614</v>
       </c>
       <c r="U19" t="n">
-        <v>0.2597</v>
+        <v>0.9245</v>
       </c>
       <c r="V19" t="n">
-        <v>-1.3505</v>
+        <v>-2.7009</v>
       </c>
       <c r="W19" t="n">
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-1.3505</v>
+        <v>-2.7009</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>E. OGUNFOLU</t>
+          <t>G. GUERRA LOZANO</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-6.2238</v>
+        <v>-6.2636</v>
       </c>
       <c r="E20" t="n">
-        <v>-3.4891</v>
+        <v>-2.2082</v>
       </c>
       <c r="F20" t="n">
-        <v>-2.7347</v>
+        <v>-4.0554</v>
       </c>
       <c r="G20" t="n">
-        <v>-6.7792</v>
+        <v>-5.6083</v>
       </c>
       <c r="H20" t="n">
-        <v>-2.4275</v>
+        <v>-1.6273</v>
       </c>
       <c r="I20" t="n">
-        <v>-4.3518</v>
+        <v>-3.9811</v>
       </c>
       <c r="J20" t="n">
-        <v>-4.0127</v>
+        <v>-1.772</v>
       </c>
       <c r="K20" t="n">
-        <v>-2.6338</v>
+        <v>-1.6952</v>
       </c>
       <c r="L20" t="n">
-        <v>-1.379</v>
+        <v>-0.07679999999999999</v>
       </c>
       <c r="M20" t="n">
-        <v>-2.7665</v>
+        <v>-3.8363</v>
       </c>
       <c r="N20" t="n">
-        <v>0.2063</v>
+        <v>0.0679</v>
       </c>
       <c r="O20" t="n">
-        <v>-2.9728</v>
+        <v>-3.9043</v>
       </c>
       <c r="P20" t="n">
-        <v>0.1931</v>
+        <v>1.1585</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>0.1931</v>
+        <v>1.1585</v>
       </c>
       <c r="S20" t="n">
-        <v>0.4851</v>
+        <v>-1.0345</v>
       </c>
       <c r="T20" t="n">
-        <v>0.5236</v>
+        <v>-1.0074</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.0384</v>
+        <v>-0.0271</v>
       </c>
       <c r="V20" t="n">
-        <v>-0.1228</v>
+        <v>-0.7792</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>0.5712</v>
       </c>
       <c r="X20" t="n">
-        <v>-0.1228</v>
+        <v>-1.3505</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>G. GUERRA LOZANO</t>
+          <t>E. OGUNFOLU</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-7.0331</v>
+        <v>-6.4885</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.8287</v>
+        <v>-3.9028</v>
       </c>
       <c r="F21" t="n">
-        <v>-4.2044</v>
+        <v>-2.5857</v>
       </c>
       <c r="G21" t="n">
-        <v>-5.6083</v>
+        <v>-6.7792</v>
       </c>
       <c r="H21" t="n">
-        <v>-1.6273</v>
+        <v>-2.4275</v>
       </c>
       <c r="I21" t="n">
-        <v>-3.9811</v>
+        <v>-4.3518</v>
       </c>
       <c r="J21" t="n">
-        <v>-1.772</v>
+        <v>-4.0127</v>
       </c>
       <c r="K21" t="n">
-        <v>-1.6952</v>
+        <v>-2.6338</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.07679999999999999</v>
+        <v>-1.379</v>
       </c>
       <c r="M21" t="n">
-        <v>-3.8363</v>
+        <v>-2.7665</v>
       </c>
       <c r="N21" t="n">
-        <v>0.0679</v>
+        <v>0.2063</v>
       </c>
       <c r="O21" t="n">
-        <v>-3.9043</v>
+        <v>-2.9728</v>
       </c>
       <c r="P21" t="n">
-        <v>1.1585</v>
+        <v>0.1931</v>
       </c>
       <c r="Q21" t="n">
         <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>1.1585</v>
+        <v>0.1931</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.804</v>
+        <v>0.2204</v>
       </c>
       <c r="T21" t="n">
-        <v>-1.6279</v>
+        <v>0.1099</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.1761</v>
+        <v>0.1105</v>
       </c>
       <c r="V21" t="n">
-        <v>-0.7792</v>
+        <v>-0.1228</v>
       </c>
       <c r="W21" t="n">
-        <v>0.5712</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-1.3505</v>
+        <v>-0.1228</v>
       </c>
     </row>
     <row r="22">
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-7.7159</v>
+        <v>-7.058</v>
       </c>
       <c r="E22" t="n">
-        <v>-5.0802</v>
+        <v>-4.77</v>
       </c>
       <c r="F22" t="n">
-        <v>-2.6357</v>
+        <v>-2.2881</v>
       </c>
       <c r="G22" t="n">
         <v>-7.1865</v>
@@ -2170,13 +2170,13 @@
         <v>1.1585</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.9822</v>
+        <v>-0.3243</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.8004</v>
+        <v>-0.4902</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.1818</v>
+        <v>0.1658</v>
       </c>
       <c r="V22" t="n">
         <v>1.2251</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-45.2702</v>
+        <v>-45.2704</v>
       </c>
       <c r="E23" t="n">
-        <v>-21.2803</v>
+        <v>-21.2805</v>
       </c>
       <c r="F23" t="n">
-        <v>-23.9899</v>
+        <v>-23.9898</v>
       </c>
       <c r="G23" t="n">
         <v>-38.4469</v>
@@ -2227,7 +2227,7 @@
         <v>-8.957100000000001</v>
       </c>
       <c r="L23" t="n">
-        <v>-6.2731</v>
+        <v>-6.273099999999999</v>
       </c>
       <c r="M23" t="n">
         <v>-23.2169</v>
@@ -2239,7 +2239,7 @@
         <v>-24.9355</v>
       </c>
       <c r="P23" t="n">
-        <v>-0.9652999999999996</v>
+        <v>-0.9652999999999998</v>
       </c>
       <c r="Q23" t="n">
         <v>-6.7578</v>
@@ -2251,19 +2251,19 @@
         <v>-1.5185</v>
       </c>
       <c r="T23" t="n">
-        <v>-3.176299999999999</v>
+        <v>-3.1762</v>
       </c>
       <c r="U23" t="n">
-        <v>1.6578</v>
+        <v>1.6577</v>
       </c>
       <c r="V23" t="n">
-        <v>-4.339499999999999</v>
+        <v>-4.3395</v>
       </c>
       <c r="W23" t="n">
         <v>3.8834</v>
       </c>
       <c r="X23" t="n">
-        <v>-8.223000000000001</v>
+        <v>-8.222999999999999</v>
       </c>
     </row>
   </sheetData>
